--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Colorado-Drywall-Supply\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BE8A39E-B994-449E-87E2-58D5EE7F28D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21435129-1F80-42A5-8630-FAB81DCB0472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="38">
   <si>
     <t>Company Name</t>
   </si>
@@ -526,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -602,7 +602,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>18</v>
       </c>
@@ -755,7 +755,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -850,7 +850,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>18</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H26" s="2"/>
       <c r="I26" s="1"/>
       <c r="J26" s="2"/>
@@ -1317,7 +1317,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>18</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>18</v>
       </c>
@@ -1695,48 +1695,27 @@
         <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H46" s="2">
-        <v>0</v>
+        <v>1.273148148148148E-4</v>
       </c>
       <c r="I46" s="1">
         <v>46237.67696759259</v>
       </c>
       <c r="J46" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B47" t="s">
-        <v>18</v>
-      </c>
-      <c r="C47">
-        <v>5644</v>
-      </c>
-      <c r="D47" t="s">
-        <v>21</v>
-      </c>
-      <c r="F47" t="s">
-        <v>16</v>
-      </c>
-      <c r="G47" t="s">
-        <v>13</v>
-      </c>
-      <c r="H47" s="2">
-        <v>0</v>
-      </c>
-      <c r="I47" s="1">
-        <v>46237.677662037036</v>
-      </c>
-      <c r="J47" s="2">
-        <v>0</v>
-      </c>
+      <c r="H47" s="2"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="2"/>
       <c r="K47" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
@@ -1744,25 +1723,25 @@
         <v>18</v>
       </c>
       <c r="C48">
-        <v>5641</v>
+        <v>5644</v>
       </c>
       <c r="D48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H48" s="2">
-        <v>1.3946759259259259E-2</v>
+        <v>0</v>
       </c>
       <c r="I48" s="1">
-        <v>46237.678356481483</v>
+        <v>46237.677662037036</v>
       </c>
       <c r="J48" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>11</v>
@@ -1773,19 +1752,19 @@
         <v>18</v>
       </c>
       <c r="C49">
-        <v>5629</v>
+        <v>5641</v>
       </c>
       <c r="D49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F49" t="s">
         <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H49" s="2">
-        <v>0</v>
+        <v>1.3946759259259259E-2</v>
       </c>
       <c r="I49" s="1">
         <v>46237.678356481483</v>
@@ -1802,10 +1781,10 @@
         <v>18</v>
       </c>
       <c r="C50">
-        <v>5630</v>
+        <v>5629</v>
       </c>
       <c r="D50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
@@ -1817,10 +1796,10 @@
         <v>0</v>
       </c>
       <c r="I50" s="1">
-        <v>46237.679050925923</v>
+        <v>46237.678356481483</v>
       </c>
       <c r="J50" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>11</v>
@@ -1831,22 +1810,22 @@
         <v>18</v>
       </c>
       <c r="C51">
-        <v>5645</v>
+        <v>5630</v>
       </c>
       <c r="D51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F51" t="s">
         <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H51" s="2">
-        <v>0</v>
+        <v>8.611111111111111E-3</v>
       </c>
       <c r="I51" s="1">
-        <v>46237.679745370369</v>
+        <v>46237.679050925923</v>
       </c>
       <c r="J51" s="2">
         <v>0</v>
@@ -1856,51 +1835,51 @@
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H52" s="2"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="2"/>
+      <c r="B52" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52">
+        <v>5645</v>
+      </c>
+      <c r="D52" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" t="s">
+        <v>16</v>
+      </c>
+      <c r="G52" t="s">
+        <v>14</v>
+      </c>
+      <c r="H52" s="2">
+        <v>0</v>
+      </c>
+      <c r="I52" s="1">
+        <v>46237.679745370369</v>
+      </c>
+      <c r="J52" s="2">
+        <v>3</v>
+      </c>
       <c r="K52" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H53" s="2"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B53" t="s">
-        <v>18</v>
-      </c>
-      <c r="C53">
-        <v>5646</v>
-      </c>
-      <c r="D53" t="s">
-        <v>26</v>
-      </c>
-      <c r="F53" t="s">
-        <v>16</v>
-      </c>
-      <c r="G53" t="s">
-        <v>13</v>
-      </c>
-      <c r="H53" s="2">
-        <v>0</v>
-      </c>
-      <c r="I53" s="1">
-        <v>46237.680439814816</v>
-      </c>
-      <c r="J53" s="2">
-        <v>0</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>18</v>
       </c>
       <c r="C54">
-        <v>5945</v>
+        <v>5646</v>
       </c>
       <c r="D54" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F54" t="s">
         <v>16</v>
@@ -1915,7 +1894,7 @@
         <v>46237.680439814816</v>
       </c>
       <c r="J54" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>11</v>
@@ -1926,25 +1905,25 @@
         <v>18</v>
       </c>
       <c r="C55">
-        <v>5635</v>
+        <v>5945</v>
       </c>
       <c r="D55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F55" t="s">
         <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H55" s="2">
-        <v>1.3287037037037036E-2</v>
+        <v>0</v>
       </c>
       <c r="I55" s="1">
-        <v>46237.681134259263</v>
+        <v>46237.680439814816</v>
       </c>
       <c r="J55" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>11</v>
@@ -1955,22 +1934,22 @@
         <v>18</v>
       </c>
       <c r="C56">
-        <v>5632</v>
+        <v>5635</v>
       </c>
       <c r="D56" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F56" t="s">
         <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H56" s="2">
-        <v>0</v>
+        <v>1.3287037037037036E-2</v>
       </c>
       <c r="I56" s="1">
-        <v>46237.681828703702</v>
+        <v>46237.681134259263</v>
       </c>
       <c r="J56" s="2">
         <v>0</v>
@@ -1984,25 +1963,25 @@
         <v>18</v>
       </c>
       <c r="C57">
-        <v>5929</v>
+        <v>5632</v>
       </c>
       <c r="D57" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F57" t="s">
         <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H57" s="2">
-        <v>9.9421296296296289E-3</v>
+        <v>0</v>
       </c>
       <c r="I57" s="1">
         <v>46237.681828703702</v>
       </c>
       <c r="J57" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>11</v>
@@ -2013,22 +1992,22 @@
         <v>18</v>
       </c>
       <c r="C58">
-        <v>5647</v>
+        <v>5929</v>
       </c>
       <c r="D58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F58" t="s">
         <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H58" s="2">
-        <v>0</v>
+        <v>9.9421296296296289E-3</v>
       </c>
       <c r="I58" s="1">
-        <v>46237.682523148149</v>
+        <v>46237.681828703702</v>
       </c>
       <c r="J58" s="2">
         <v>0</v>
@@ -2042,36 +2021,57 @@
         <v>18</v>
       </c>
       <c r="C59">
-        <v>5640</v>
+        <v>5647</v>
       </c>
       <c r="D59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F59" t="s">
         <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H59" s="2">
-        <v>5.4050925925925924E-3</v>
+        <v>0</v>
       </c>
       <c r="I59" s="1">
-        <v>46237.683217592596</v>
+        <v>46237.682523148149</v>
       </c>
       <c r="J59" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K59" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H60" s="2"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="2"/>
+      <c r="B60" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60">
+        <v>5640</v>
+      </c>
+      <c r="D60" t="s">
+        <v>32</v>
+      </c>
+      <c r="F60" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" t="s">
+        <v>10</v>
+      </c>
+      <c r="H60" s="2">
+        <v>1.173611111111111E-2</v>
+      </c>
+      <c r="I60" s="1">
+        <v>46237.683217592596</v>
+      </c>
+      <c r="J60" s="2">
+        <v>1</v>
+      </c>
       <c r="K60" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
@@ -2097,7 +2097,7 @@
         <v>46237.683912037035</v>
       </c>
       <c r="J61" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K61" s="1" t="s">
         <v>11</v>
@@ -2184,7 +2184,7 @@
         <v>46237.685300925928</v>
       </c>
       <c r="J64" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K64" s="1" t="s">
         <v>11</v>
@@ -2204,16 +2204,16 @@
         <v>16</v>
       </c>
       <c r="G65" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H65" s="2">
-        <v>0</v>
+        <v>2.3148148148148147E-3</v>
       </c>
       <c r="I65" s="1">
         <v>46237.685995370368</v>
       </c>
       <c r="J65" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K65" s="1" t="s">
         <v>11</v>
@@ -2223,7 +2223,9 @@
       <c r="H66" s="2"/>
       <c r="I66" s="1"/>
       <c r="J66" s="2"/>
-      <c r="K66" s="1"/>
+      <c r="K66" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H67" s="2"/>
@@ -2267,7 +2269,7 @@
       <c r="J73" s="2"/>
       <c r="K73" s="1"/>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H74" s="2"/>
       <c r="I74" s="1"/>
       <c r="J74" s="2"/>
@@ -2315,7 +2317,7 @@
       <c r="J81" s="2"/>
       <c r="K81" s="1"/>
     </row>
-    <row r="82" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H82" s="2"/>
       <c r="I82" s="1"/>
       <c r="J82" s="2"/>
@@ -2375,7 +2377,7 @@
       <c r="J91" s="2"/>
       <c r="K91" s="1"/>
     </row>
-    <row r="92" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H92" s="2"/>
       <c r="I92" s="1"/>
       <c r="J92" s="2"/>
@@ -2495,7 +2497,7 @@
       <c r="J111" s="2"/>
       <c r="K111" s="1"/>
     </row>
-    <row r="112" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H112" s="2"/>
       <c r="I112" s="1"/>
       <c r="J112" s="2"/>
@@ -2513,7 +2515,7 @@
       <c r="J114" s="2"/>
       <c r="K114" s="1"/>
     </row>
-    <row r="115" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H115" s="2"/>
       <c r="I115" s="1"/>
       <c r="J115" s="2"/>
@@ -2585,7 +2587,7 @@
       <c r="J126" s="2"/>
       <c r="K126" s="1"/>
     </row>
-    <row r="127" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H127" s="2"/>
       <c r="I127" s="1"/>
       <c r="J127" s="2"/>
@@ -2867,7 +2869,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
       <c r="J174" s="2"/>
@@ -2897,7 +2899,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
     </row>
-    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -2957,7 +2959,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -3065,7 +3067,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -3257,7 +3259,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -3773,7 +3775,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -3839,7 +3841,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -3851,7 +3853,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -3947,7 +3949,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -3959,7 +3961,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -4055,7 +4057,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -4115,7 +4117,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -43068,6 +43070,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -43360,6 +43363,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -43670,6 +43675,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -43794,6 +43800,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -43805,6 +43812,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -43953,6 +43961,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -43963,10 +43972,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -44000,15 +44011,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -44049,18 +44063,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -44076,6 +44094,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -44085,10 +44104,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -44124,10 +44145,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -44153,6 +44176,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -44167,6 +44191,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -44201,6 +44226,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -44210,6 +44236,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -44219,6 +44246,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -44233,15 +44261,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -44271,6 +44300,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -44291,11 +44321,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -44304,6 +44336,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -44333,6 +44366,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -44342,10 +44376,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -44360,14 +44396,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -44387,10 +44426,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -44410,9 +44451,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -44447,18 +44491,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -44473,12 +44521,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -44493,10 +44541,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -44516,6 +44566,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -44535,6 +44586,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -44544,6 +44596,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -44589,6 +44642,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -44598,6 +44652,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -44612,6 +44667,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -44621,10 +44677,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -44639,6 +44697,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -44648,6 +44707,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -44667,6 +44727,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -44686,10 +44747,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -44699,6 +44762,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -44709,10 +44773,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -44727,18 +44793,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -44758,10 +44828,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -44781,6 +44853,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -44811,7 +44884,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -44826,10 +44898,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -44844,6 +44918,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -44858,11 +44933,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -44872,6 +44947,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -44887,6 +44963,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -44901,6 +44978,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -44921,6 +44999,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -44946,11 +45025,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -44969,15 +45050,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -44987,6 +45069,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -45006,6 +45089,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -45020,6 +45104,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -45039,10 +45124,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -45052,6 +45139,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -45062,6 +45150,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -45098,7 +45187,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -45107,6 +45195,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -45120,10 +45209,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Colorado-Drywall-Supply\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21435129-1F80-42A5-8630-FAB81DCB0472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0337D8FA-979D-435D-B866-581782592FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -526,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7403"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -602,7 +602,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>18</v>
       </c>
@@ -755,7 +755,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -850,7 +850,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>18</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H26" s="2"/>
       <c r="I26" s="1"/>
       <c r="J26" s="2"/>
@@ -1317,7 +1317,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>18</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>18</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>12</v>
       </c>
       <c r="H46" s="2">
-        <v>1.273148148148148E-4</v>
+        <v>3.7384259259259259E-3</v>
       </c>
       <c r="I46" s="1">
         <v>46237.67696759259</v>
@@ -1871,7 +1871,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>18</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>12</v>
       </c>
       <c r="H65" s="2">
-        <v>2.3148148148148147E-3</v>
+        <v>1.607638888888889E-2</v>
       </c>
       <c r="I65" s="1">
         <v>46237.685995370368</v>
@@ -2269,7 +2269,7 @@
       <c r="J73" s="2"/>
       <c r="K73" s="1"/>
     </row>
-    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H74" s="2"/>
       <c r="I74" s="1"/>
       <c r="J74" s="2"/>
@@ -2317,7 +2317,7 @@
       <c r="J81" s="2"/>
       <c r="K81" s="1"/>
     </row>
-    <row r="82" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H82" s="2"/>
       <c r="I82" s="1"/>
       <c r="J82" s="2"/>
@@ -2377,7 +2377,7 @@
       <c r="J91" s="2"/>
       <c r="K91" s="1"/>
     </row>
-    <row r="92" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H92" s="2"/>
       <c r="I92" s="1"/>
       <c r="J92" s="2"/>
@@ -2497,7 +2497,7 @@
       <c r="J111" s="2"/>
       <c r="K111" s="1"/>
     </row>
-    <row r="112" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H112" s="2"/>
       <c r="I112" s="1"/>
       <c r="J112" s="2"/>
@@ -2515,7 +2515,7 @@
       <c r="J114" s="2"/>
       <c r="K114" s="1"/>
     </row>
-    <row r="115" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H115" s="2"/>
       <c r="I115" s="1"/>
       <c r="J115" s="2"/>
@@ -2587,7 +2587,7 @@
       <c r="J126" s="2"/>
       <c r="K126" s="1"/>
     </row>
-    <row r="127" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H127" s="2"/>
       <c r="I127" s="1"/>
       <c r="J127" s="2"/>
@@ -2869,7 +2869,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
       <c r="J174" s="2"/>
@@ -2899,7 +2899,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
     </row>
-    <row r="179" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -2959,7 +2959,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -3067,7 +3067,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -3259,7 +3259,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -3775,7 +3775,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -3841,7 +3841,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -3853,7 +3853,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -3949,7 +3949,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -3961,7 +3961,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -4057,7 +4057,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -4117,7 +4117,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -43070,7 +43070,6 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -43363,8 +43362,6 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7055" s="2"/>
-      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -43675,7 +43672,6 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -43800,7 +43796,6 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -43812,7 +43807,6 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -43961,35 +43955,29 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -44000,44 +43988,35 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7162" s="2"/>
-      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -44048,37 +44027,30 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -44089,52 +44061,42 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -44145,17 +44107,14 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -44166,32 +44125,26 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -44201,106 +44154,86 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7201" s="2"/>
+    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7202" s="2"/>
+    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7203" s="2"/>
+    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7204" s="2"/>
+    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7205" s="2"/>
+    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7206" s="2"/>
+    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7207" s="2"/>
+    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7208" s="2"/>
+    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7209" s="2"/>
+    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7210" s="2"/>
+    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7211" s="2"/>
+    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7212" s="2"/>
+    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7214" s="2"/>
+    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7215" s="2"/>
+    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7216" s="2"/>
+    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -44310,7 +44243,6 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -44321,127 +44253,101 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7225" s="2"/>
-      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7233" s="2"/>
+    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7234" s="2"/>
+    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7235" s="2"/>
+    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7236" s="2"/>
+    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7237" s="2"/>
+    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7238" s="2"/>
+    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7239" s="2"/>
+    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7240" s="2"/>
+    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7241" s="2"/>
+    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7242" s="2"/>
+    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7243" s="2"/>
+    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7244" s="2"/>
+    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7245" s="2"/>
+    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7246" s="2"/>
+    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7247" s="2"/>
+    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7248" s="2"/>
+    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -44451,62 +44357,49 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7251" s="2"/>
-      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -44526,67 +44419,54 @@
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -44596,38 +44476,31 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -44642,117 +44515,94 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -44761,99 +44611,80 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7313" s="2"/>
+    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7314" s="2"/>
+    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7315" s="2"/>
+    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7316" s="2"/>
+    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7317" s="2"/>
+    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7318" s="2"/>
+    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7319" s="2"/>
+    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7320" s="2"/>
+    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7321" s="2"/>
+    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7322" s="2"/>
+    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7323" s="2"/>
+    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7324" s="2"/>
+    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7325" s="2"/>
+    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7326" s="2"/>
+    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7327" s="2"/>
+    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7328" s="2"/>
+    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -44863,23 +44694,19 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
@@ -44888,52 +44715,42 @@
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
@@ -44947,38 +44764,31 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -44988,7 +44798,6 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -44999,23 +44808,19 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -45025,37 +44830,30 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
@@ -45064,72 +44862,58 @@
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -45139,76 +44923,51 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7393" s="2"/>
+    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7394" s="1"/>
+    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7395" s="2"/>
+    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7396" s="2"/>
+    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7397" s="2"/>
+    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7399" s="2"/>
-      <c r="I7399" s="1"/>
+    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7400" s="2"/>
-      <c r="I7400" s="1"/>
+    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7400" s="1"/>
-    </row>
-    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7401" s="2"/>
-      <c r="I7401" s="1"/>
-    </row>
-    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7402" s="2"/>
-      <c r="I7402" s="1"/>
-    </row>
-    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7403" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Colorado-Drywall-Supply\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0337D8FA-979D-435D-B866-581782592FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF782833-CA8A-4983-92B1-CED5CFBFC9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -526,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7400"/>
+  <dimension ref="A1:K7401"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -43070,6 +43070,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -43362,6 +43363,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -43672,6 +43675,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -43796,6 +43800,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -43807,6 +43812,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -43955,29 +43961,35 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -43988,35 +44000,44 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -44027,30 +44048,37 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -44061,42 +44089,52 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -44107,14 +44145,17 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -44125,26 +44166,32 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -44154,86 +44201,107 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -44243,6 +44311,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -44253,101 +44322,127 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -44357,49 +44452,62 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -44414,59 +44522,73 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -44476,31 +44598,38 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -44510,99 +44639,123 @@
       <c r="K7287" s="1"/>
     </row>
     <row r="7288" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7288" s="2"/>
       <c r="I7288" s="1"/>
       <c r="J7288" s="2"/>
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -44611,80 +44764,99 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -44694,67 +44866,83 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -44764,31 +44952,38 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -44798,6 +44993,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -44808,19 +45004,23 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -44830,90 +45030,112 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -44923,51 +45145,71 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7394" s="2"/>
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7398" s="2"/>
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
